--- a/tabela_produtos_site.xlsx
+++ b/tabela_produtos_site.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0925d356f97d17c9/Desktop/special-summer-sale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="412" documentId="11_1479D0EED2335F840378C78657AD3C1B78FA1F78" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FB63922-D19B-4369-BD9E-6AB6B26030A5}"/>
+  <xr:revisionPtr revIDLastSave="460" documentId="11_1479D0EED2335F840378C78657AD3C1B78FA1F78" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE56C006-6895-4636-BA08-D53162748D67}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="547">
   <si>
     <t>categoria</t>
   </si>
@@ -83,9 +84,6 @@
     <t>Cadeira Melia</t>
   </si>
   <si>
-    <t>R$ 957,00</t>
-  </si>
-  <si>
     <t>Cadeira Claudia</t>
   </si>
   <si>
@@ -168,9 +166,6 @@
   </si>
   <si>
     <t>Cadeira press</t>
-  </si>
-  <si>
-    <t>R$ 2.670,00</t>
   </si>
   <si>
     <t>Cadeira Piaf</t>
@@ -2617,7 +2612,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -2626,7 +2621,7 @@
         <v>7</v>
       </c>
       <c r="Q1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -2642,7 +2637,7 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
@@ -2676,8 +2671,8 @@
       <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>16</v>
+      <c r="D3" s="11">
+        <v>1190</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1">
@@ -2685,7 +2680,7 @@
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -2699,7 +2694,7 @@
         <v>12</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q3" s="1">
         <v>8</v>
@@ -2712,21 +2707,21 @@
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2738,7 +2733,7 @@
         <v>12</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="1">
         <v>2</v>
@@ -2751,13 +2746,13 @@
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1">
@@ -2765,7 +2760,7 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -2779,7 +2774,7 @@
         <v>12</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="1">
         <v>3</v>
@@ -2792,21 +2787,21 @@
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>29</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -2818,7 +2813,7 @@
         <v>12</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -2831,21 +2826,21 @@
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>33</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -2857,7 +2852,7 @@
         <v>12</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q7" s="1">
         <v>1</v>
@@ -2870,13 +2865,13 @@
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
@@ -2884,7 +2879,7 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -2898,7 +2893,7 @@
         <v>12</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q8" s="1">
         <v>2</v>
@@ -2911,13 +2906,13 @@
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
@@ -2925,7 +2920,7 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2937,7 +2932,7 @@
         <v>12</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q9" s="1">
         <v>2</v>
@@ -2950,13 +2945,13 @@
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>45</v>
+      <c r="D10" s="11">
+        <v>3120</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
@@ -2964,7 +2959,7 @@
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -2978,7 +2973,7 @@
         <v>12</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="1">
         <v>2</v>
@@ -2991,13 +2986,13 @@
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
@@ -3005,7 +3000,7 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -3019,7 +3014,7 @@
         <v>12</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q11" s="1">
         <v>1</v>
@@ -3032,21 +3027,21 @@
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -3073,13 +3068,13 @@
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1">
@@ -3087,7 +3082,7 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -3101,7 +3096,7 @@
         <v>12</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="1">
         <v>2</v>
@@ -3114,21 +3109,21 @@
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
@@ -3142,7 +3137,7 @@
         <v>12</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q14" s="1">
         <v>2</v>
@@ -3155,21 +3150,21 @@
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>65</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -3183,7 +3178,7 @@
         <v>12</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q15" s="1">
         <v>1</v>
@@ -3196,21 +3191,21 @@
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -3222,7 +3217,7 @@
         <v>12</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="1">
         <v>1</v>
@@ -3235,13 +3230,13 @@
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>73</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1">
@@ -3249,7 +3244,7 @@
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
@@ -3263,7 +3258,7 @@
         <v>12</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="1">
         <v>2</v>
@@ -3276,21 +3271,21 @@
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
@@ -3304,7 +3299,7 @@
         <v>12</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="1">
         <v>2</v>
@@ -3317,21 +3312,21 @@
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>81</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
@@ -3345,7 +3340,7 @@
         <v>12</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q19" s="1">
         <v>2</v>
@@ -3358,13 +3353,13 @@
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>85</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1">
@@ -3372,12 +3367,12 @@
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3386,7 +3381,7 @@
         <v>12</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="1">
         <v>1</v>
@@ -3399,21 +3394,21 @@
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -3427,7 +3422,7 @@
         <v>12</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q21" s="1">
         <v>1</v>
@@ -3440,21 +3435,21 @@
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>94</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -3468,7 +3463,7 @@
         <v>12</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="1">
         <v>2</v>
@@ -3481,21 +3476,21 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -3509,7 +3504,7 @@
         <v>12</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="1">
         <v>2</v>
@@ -3522,21 +3517,21 @@
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -3548,7 +3543,7 @@
         <v>12</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="1">
         <v>2</v>
@@ -3561,21 +3556,21 @@
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>104</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -3589,7 +3584,7 @@
         <v>12</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q25" s="1">
         <v>2</v>
@@ -3602,21 +3597,21 @@
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -3641,13 +3636,13 @@
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1">
@@ -3655,7 +3650,7 @@
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
@@ -3669,7 +3664,7 @@
         <v>12</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q27" s="1">
         <v>1</v>
@@ -3682,21 +3677,21 @@
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -3708,7 +3703,7 @@
         <v>12</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q28" s="1">
         <v>1</v>
@@ -3721,21 +3716,21 @@
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
@@ -3749,7 +3744,7 @@
         <v>12</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q29" s="1">
         <v>1</v>
@@ -3762,13 +3757,13 @@
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1">
@@ -3776,7 +3771,7 @@
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -3788,7 +3783,7 @@
         <v>12</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q30" s="1">
         <v>1</v>
@@ -3801,21 +3796,21 @@
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>130</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -3827,7 +3822,7 @@
         <v>12</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q31" s="1">
         <v>1</v>
@@ -3840,13 +3835,13 @@
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1">
@@ -3854,7 +3849,7 @@
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -3868,7 +3863,7 @@
         <v>12</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q32" s="1">
         <v>1</v>
@@ -3881,21 +3876,21 @@
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>138</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -3909,7 +3904,7 @@
         <v>12</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q33" s="1">
         <v>1</v>
@@ -3922,21 +3917,21 @@
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -3950,7 +3945,7 @@
         <v>12</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q34" s="1">
         <v>1</v>
@@ -3963,10 +3958,10 @@
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D35" s="11">
         <v>1450</v>
@@ -3975,11 +3970,11 @@
         <v>870</v>
       </c>
       <c r="F35" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -3991,7 +3986,7 @@
         <v>12</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q35" s="1">
         <v>1</v>
@@ -4004,10 +3999,10 @@
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D36" s="11">
         <v>3614</v>
@@ -4020,7 +4015,7 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -4032,7 +4027,7 @@
         <v>12</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q36" s="1">
         <v>2</v>
@@ -4045,10 +4040,10 @@
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D37" s="11">
         <v>6624</v>
@@ -4061,7 +4056,7 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -4073,7 +4068,7 @@
         <v>12</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q37" s="1">
         <v>1</v>
@@ -4086,10 +4081,10 @@
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D38" s="11">
         <v>6350</v>
@@ -4102,7 +4097,7 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -4114,7 +4109,7 @@
         <v>12</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q38" s="1">
         <v>1</v>
@@ -4127,10 +4122,10 @@
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D39" s="11">
         <v>3734</v>
@@ -4143,7 +4138,7 @@
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -4155,7 +4150,7 @@
         <v>12</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q39" s="1">
         <v>1</v>
@@ -4168,10 +4163,10 @@
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D40" s="11">
         <v>2890</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -4196,7 +4191,7 @@
         <v>12</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q40" s="1">
         <v>1</v>
@@ -4209,10 +4204,10 @@
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D41" s="11">
         <v>3455</v>
@@ -4225,7 +4220,7 @@
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -4237,7 +4232,7 @@
         <v>12</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q41" s="1">
         <v>1</v>
@@ -4250,10 +4245,10 @@
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D42" s="11">
         <v>8700</v>
@@ -4262,11 +4257,11 @@
         <v>3480</v>
       </c>
       <c r="F42" s="1">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -4278,7 +4273,7 @@
         <v>12</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q42" s="1">
         <v>1</v>
@@ -4291,10 +4286,10 @@
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D43" s="11">
         <v>4525</v>
@@ -4307,7 +4302,7 @@
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -4319,7 +4314,7 @@
         <v>12</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q43" s="1">
         <v>1</v>
@@ -4332,10 +4327,10 @@
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D44" s="11">
         <v>2750</v>
@@ -4344,11 +4339,11 @@
         <v>1650</v>
       </c>
       <c r="F44" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -4362,7 +4357,7 @@
         <v>12</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q44" s="1">
         <v>1</v>
@@ -4375,10 +4370,10 @@
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D45" s="11">
         <v>1300</v>
@@ -4387,11 +4382,11 @@
         <v>909.99999999999989</v>
       </c>
       <c r="F45" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -4403,7 +4398,7 @@
         <v>12</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q45" s="1">
         <v>1</v>
@@ -4416,13 +4411,13 @@
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D46" s="11">
-        <v>5280</v>
+        <v>5880</v>
       </c>
       <c r="E46" s="1">
         <v>2640</v>
@@ -4432,7 +4427,7 @@
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -4446,7 +4441,7 @@
         <v>12</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q46" s="1">
         <v>1</v>
@@ -4459,10 +4454,10 @@
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D47" s="11">
         <v>1455</v>
@@ -4471,11 +4466,11 @@
         <v>727.5</v>
       </c>
       <c r="F47" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -4498,10 +4493,10 @@
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D48" s="11">
         <v>3360</v>
@@ -4514,7 +4509,7 @@
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -4528,7 +4523,7 @@
         <v>12</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q48" s="1">
         <v>1</v>
@@ -4541,10 +4536,10 @@
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D49" s="11">
         <v>2600</v>
@@ -4557,7 +4552,7 @@
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -4569,7 +4564,7 @@
         <v>12</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q49" s="1">
         <v>2</v>
@@ -4582,10 +4577,10 @@
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D50" s="11">
         <v>2700</v>
@@ -4598,7 +4593,7 @@
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -4610,7 +4605,7 @@
         <v>12</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q50" s="1">
         <v>2</v>
@@ -4623,10 +4618,10 @@
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D51" s="11">
         <v>1752</v>
@@ -4635,11 +4630,11 @@
         <v>700.80000000000007</v>
       </c>
       <c r="F51" s="1">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4651,7 +4646,7 @@
         <v>12</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q51" s="1">
         <v>1</v>
@@ -4664,10 +4659,10 @@
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D52" s="11">
         <v>1590</v>
@@ -4676,11 +4671,11 @@
         <v>636</v>
       </c>
       <c r="F52" s="1">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -4692,7 +4687,7 @@
         <v>12</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q52" s="1">
         <v>1</v>
@@ -4705,10 +4700,10 @@
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D53" s="11">
         <v>1590</v>
@@ -4717,11 +4712,11 @@
         <v>954</v>
       </c>
       <c r="F53" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -4733,7 +4728,7 @@
         <v>12</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q53" s="1">
         <v>1</v>
@@ -4746,10 +4741,10 @@
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D54" s="11">
         <v>1590</v>
@@ -4758,11 +4753,11 @@
         <v>795</v>
       </c>
       <c r="F54" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4774,7 +4769,7 @@
         <v>12</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q54" s="1">
         <v>1</v>
@@ -4787,10 +4782,10 @@
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D55" s="11">
         <v>1752</v>
@@ -4803,7 +4798,7 @@
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4815,7 +4810,7 @@
         <v>12</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q55" s="1">
         <v>1</v>
@@ -4828,10 +4823,10 @@
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D56" s="11">
         <v>1560</v>
@@ -4840,11 +4835,11 @@
         <v>780</v>
       </c>
       <c r="F56" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -4856,7 +4851,7 @@
         <v>12</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q56" s="1">
         <v>1</v>
@@ -4869,10 +4864,10 @@
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D57" s="11">
         <v>2980</v>
@@ -4881,11 +4876,11 @@
         <v>1192</v>
       </c>
       <c r="F57" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -4897,7 +4892,7 @@
         <v>12</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q57" s="1">
         <v>1</v>
@@ -4910,10 +4905,10 @@
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D58" s="11">
         <v>3745</v>
@@ -4926,7 +4921,7 @@
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -4938,7 +4933,7 @@
         <v>12</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q58" s="1">
         <v>1</v>
@@ -4951,10 +4946,10 @@
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D59" s="11">
         <v>2980</v>
@@ -4967,7 +4962,7 @@
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -4981,7 +4976,7 @@
         <v>12</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q59" s="1">
         <v>1</v>
@@ -4994,10 +4989,10 @@
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D60" s="11">
         <v>980</v>
@@ -5010,7 +5005,7 @@
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -5024,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q60" s="1">
         <v>2</v>
@@ -5037,10 +5032,10 @@
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D61" s="11">
         <v>3700</v>
@@ -5053,7 +5048,7 @@
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -5065,7 +5060,7 @@
         <v>12</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q61" s="1">
         <v>1</v>
@@ -5078,10 +5073,10 @@
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D62" s="11">
         <v>670</v>
@@ -5094,7 +5089,7 @@
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -5106,7 +5101,7 @@
         <v>12</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q62" s="1">
         <v>1</v>
@@ -5119,10 +5114,10 @@
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D63" s="11">
         <v>1803</v>
@@ -5131,11 +5126,11 @@
         <v>1262.0999999999999</v>
       </c>
       <c r="F63" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -5147,7 +5142,7 @@
         <v>12</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q63" s="1">
         <v>1</v>
@@ -5160,10 +5155,10 @@
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D64" s="11">
         <v>1595</v>
@@ -5172,11 +5167,11 @@
         <v>1116.5</v>
       </c>
       <c r="F64" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -5188,7 +5183,7 @@
         <v>12</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q64" s="1">
         <v>1</v>
@@ -5201,10 +5196,10 @@
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D65" s="11">
         <v>6070</v>
@@ -5217,7 +5212,7 @@
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -5229,7 +5224,7 @@
         <v>12</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q65" s="1">
         <v>1</v>
@@ -5242,10 +5237,10 @@
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D66" s="11">
         <v>28588</v>
@@ -5254,11 +5249,11 @@
         <v>11435.2</v>
       </c>
       <c r="F66" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -5270,7 +5265,7 @@
         <v>12</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q66" s="1">
         <v>1</v>
@@ -5283,10 +5278,10 @@
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D67" s="11">
         <v>9674</v>
@@ -5299,7 +5294,7 @@
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -5313,7 +5308,7 @@
         <v>12</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q67" s="1">
         <v>1</v>
@@ -5326,10 +5321,10 @@
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D68" s="11">
         <v>16358</v>
@@ -5338,11 +5333,11 @@
         <v>8179</v>
       </c>
       <c r="F68" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
@@ -5356,7 +5351,7 @@
         <v>12</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q68" s="1">
         <v>1</v>
@@ -5369,10 +5364,10 @@
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D69" s="11">
         <v>7570</v>
@@ -5381,11 +5376,11 @@
         <v>3028</v>
       </c>
       <c r="F69" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
@@ -5399,7 +5394,7 @@
         <v>12</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q69" s="1">
         <v>1</v>
@@ -5412,10 +5407,10 @@
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D70" s="11">
         <v>7890</v>
@@ -5426,7 +5421,7 @@
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -5438,7 +5433,7 @@
         <v>12</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q70" s="1">
         <v>1</v>
@@ -5451,10 +5446,10 @@
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D71" s="11">
         <v>4648</v>
@@ -5465,7 +5460,7 @@
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -5479,7 +5474,7 @@
         <v>12</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q71" s="1">
         <v>1</v>
@@ -5492,21 +5487,21 @@
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D72" s="11">
         <v>2850</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -5520,7 +5515,7 @@
         <v>12</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q72" s="1">
         <v>1</v>
@@ -5533,10 +5528,10 @@
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D73" s="11">
         <v>4580</v>
@@ -5547,7 +5542,7 @@
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -5559,7 +5554,7 @@
         <v>12</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q73" s="1">
         <v>1</v>
@@ -5572,10 +5567,10 @@
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D74" s="11">
         <v>3975</v>
@@ -5586,7 +5581,7 @@
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -5598,7 +5593,7 @@
         <v>12</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q74" s="1">
         <v>1</v>
@@ -5611,10 +5606,10 @@
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D75" s="11">
         <v>4400</v>
@@ -5625,7 +5620,7 @@
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -5639,7 +5634,7 @@
         <v>12</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q75" s="1">
         <v>1</v>
@@ -5652,10 +5647,10 @@
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D76" s="11">
         <v>5720</v>
@@ -5666,21 +5661,21 @@
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="O76" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q76" s="1">
         <v>0</v>
@@ -5693,10 +5688,10 @@
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D77" s="11">
         <v>7440</v>
@@ -5707,21 +5702,21 @@
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="O77" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q77" s="1">
         <v>0</v>
@@ -5734,10 +5729,10 @@
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D78" s="11">
         <v>2750</v>
@@ -5748,7 +5743,7 @@
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -5760,7 +5755,7 @@
         <v>12</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q78" s="1">
         <v>2</v>
@@ -5773,10 +5768,10 @@
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D79" s="11">
         <v>12720</v>
@@ -5787,7 +5782,7 @@
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -5799,7 +5794,7 @@
         <v>12</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q79" s="1">
         <v>1</v>
@@ -5812,10 +5807,10 @@
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D80" s="11">
         <v>1780</v>
@@ -5826,7 +5821,7 @@
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -5838,7 +5833,7 @@
         <v>12</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q80" s="1">
         <v>1</v>
@@ -5851,21 +5846,21 @@
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D81" s="11">
         <v>1720</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -5877,7 +5872,7 @@
         <v>12</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q81" s="1">
         <v>4</v>
@@ -5890,21 +5885,21 @@
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D82" s="11">
         <v>9768</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -5916,7 +5911,7 @@
         <v>12</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q82" s="1">
         <v>1</v>
@@ -5929,10 +5924,10 @@
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D83" s="11">
         <v>1678</v>
@@ -5943,7 +5938,7 @@
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -5955,7 +5950,7 @@
         <v>12</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q83" s="1">
         <v>1</v>
@@ -5968,10 +5963,10 @@
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D84" s="11">
         <v>3970</v>
@@ -5982,7 +5977,7 @@
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -5994,7 +5989,7 @@
         <v>12</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q84" s="1">
         <v>1</v>
@@ -6007,10 +6002,10 @@
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D85" s="11">
         <v>533</v>
@@ -6021,7 +6016,7 @@
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -6033,7 +6028,7 @@
         <v>12</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q85" s="1">
         <v>4</v>
@@ -6046,23 +6041,23 @@
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D86" s="11">
         <v>1152</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -6076,7 +6071,7 @@
         <v>12</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q86" s="1">
         <v>1</v>
@@ -6089,10 +6084,10 @@
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D87" s="11">
         <v>2888</v>
@@ -6103,7 +6098,7 @@
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -6115,7 +6110,7 @@
         <v>12</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q87" s="1">
         <v>50</v>
@@ -6128,10 +6123,10 @@
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D88" s="11">
         <v>1055</v>
@@ -6142,7 +6137,7 @@
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -6154,7 +6149,7 @@
         <v>12</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q88" s="1">
         <v>100</v>
@@ -6167,21 +6162,21 @@
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D89" s="11">
         <v>18321</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -6197,7 +6192,7 @@
         <v>12</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q89" s="1">
         <v>1</v>
@@ -6210,10 +6205,10 @@
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D90" s="11">
         <v>1247</v>
@@ -6224,7 +6219,7 @@
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -6236,7 +6231,7 @@
         <v>12</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q90" s="1">
         <v>2</v>
@@ -6249,10 +6244,10 @@
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D91" s="11"/>
       <c r="E91" s="1">
@@ -6263,7 +6258,7 @@
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -6275,7 +6270,7 @@
         <v>12</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q91" s="1">
         <v>2</v>
@@ -6288,21 +6283,21 @@
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="1">
         <v>864.5</v>
       </c>
       <c r="F92" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -6314,7 +6309,7 @@
         <v>12</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q92" s="1">
         <v>1</v>
@@ -6327,21 +6322,21 @@
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D93" s="11"/>
       <c r="E93" s="1">
         <v>717.5</v>
       </c>
       <c r="F93" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -6353,7 +6348,7 @@
         <v>12</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q93" s="1">
         <v>1</v>
@@ -6366,10 +6361,10 @@
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="1">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
@@ -6392,7 +6387,7 @@
         <v>12</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q94" s="1">
         <v>1</v>
@@ -6405,21 +6400,21 @@
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D95" s="11"/>
       <c r="E95" s="1">
         <v>1475</v>
       </c>
       <c r="F95" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -6431,7 +6426,7 @@
         <v>12</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q95" s="1">
         <v>1</v>
@@ -6444,10 +6439,10 @@
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D96" s="11"/>
       <c r="E96" s="1">
@@ -6458,7 +6453,7 @@
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -6470,7 +6465,7 @@
         <v>12</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q96" s="1">
         <v>1</v>
@@ -6483,10 +6478,10 @@
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D97" s="11"/>
       <c r="E97" s="1">
@@ -6497,7 +6492,7 @@
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -6509,7 +6504,7 @@
         <v>12</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q97" s="1">
         <v>1</v>
@@ -6522,10 +6517,10 @@
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D98" s="11"/>
       <c r="E98" s="1">
@@ -6536,7 +6531,7 @@
       </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -6548,7 +6543,7 @@
         <v>12</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q98" s="1">
         <v>1</v>
@@ -6561,10 +6556,10 @@
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D99" s="11"/>
       <c r="E99" s="1">
@@ -6575,7 +6570,7 @@
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -6587,7 +6582,7 @@
         <v>12</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q99" s="1">
         <v>1</v>
@@ -6600,10 +6595,10 @@
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D100" s="11"/>
       <c r="E100" s="1">
@@ -6614,7 +6609,7 @@
       </c>
       <c r="G100" s="1"/>
       <c r="H100" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -6626,7 +6621,7 @@
         <v>12</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q100" s="1">
         <v>1</v>
@@ -6639,10 +6634,10 @@
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D101" s="11"/>
       <c r="E101" s="1">
@@ -6653,7 +6648,7 @@
       </c>
       <c r="G101" s="1"/>
       <c r="H101" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -6665,7 +6660,7 @@
         <v>12</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q101" s="1">
         <v>1</v>
@@ -6678,10 +6673,10 @@
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D102" s="11"/>
       <c r="E102" s="1">
@@ -6692,7 +6687,7 @@
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -6704,7 +6699,7 @@
         <v>12</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q102" s="1">
         <v>1</v>
@@ -6717,10 +6712,10 @@
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D103" s="11"/>
       <c r="E103" s="1">
@@ -6731,7 +6726,7 @@
       </c>
       <c r="G103" s="1"/>
       <c r="H103" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -6743,7 +6738,7 @@
         <v>12</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q103" s="1">
         <v>1</v>
@@ -6756,10 +6751,10 @@
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D104" s="11"/>
       <c r="E104" s="1">
@@ -6770,7 +6765,7 @@
       </c>
       <c r="G104" s="1"/>
       <c r="H104" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -6782,7 +6777,7 @@
         <v>12</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q104" s="1">
         <v>1</v>
@@ -6795,10 +6790,10 @@
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D105" s="11"/>
       <c r="E105" s="1">
@@ -6809,7 +6804,7 @@
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -6821,7 +6816,7 @@
         <v>12</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q105" s="1">
         <v>1</v>
@@ -6834,10 +6829,10 @@
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="1">
@@ -6848,7 +6843,7 @@
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -6860,7 +6855,7 @@
         <v>12</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q106" s="1">
         <v>1</v>
@@ -6873,10 +6868,10 @@
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D107" s="11"/>
       <c r="E107" s="1">
@@ -6887,7 +6882,7 @@
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -6899,7 +6894,7 @@
         <v>12</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q107" s="1">
         <v>1</v>
@@ -6912,10 +6907,10 @@
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D108" s="11"/>
       <c r="E108" s="1">
@@ -6926,7 +6921,7 @@
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -6938,7 +6933,7 @@
         <v>12</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q108" s="1">
         <v>1</v>
@@ -6951,10 +6946,10 @@
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D109" s="11"/>
       <c r="E109" s="1">
@@ -6965,7 +6960,7 @@
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6977,7 +6972,7 @@
         <v>12</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q109" s="1">
         <v>1</v>
@@ -6990,10 +6985,10 @@
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D110" s="11"/>
       <c r="E110" s="1">
@@ -7004,7 +6999,7 @@
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -7016,7 +7011,7 @@
         <v>12</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q110" s="1">
         <v>1</v>
@@ -7029,10 +7024,10 @@
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D111" s="11"/>
       <c r="E111" s="1">
@@ -7043,7 +7038,7 @@
       </c>
       <c r="G111" s="1"/>
       <c r="H111" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -7055,7 +7050,7 @@
         <v>12</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q111" s="1">
         <v>1</v>
@@ -7068,10 +7063,10 @@
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D112" s="11"/>
       <c r="E112" s="1">
@@ -7082,7 +7077,7 @@
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -7094,7 +7089,7 @@
         <v>12</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q112" s="1">
         <v>1</v>
@@ -7107,10 +7102,10 @@
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="1">
@@ -7121,7 +7116,7 @@
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -7133,7 +7128,7 @@
         <v>12</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q113" s="1">
         <v>1</v>
@@ -7146,10 +7141,10 @@
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="1">
@@ -7160,7 +7155,7 @@
       </c>
       <c r="G114" s="1"/>
       <c r="H114" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -7172,7 +7167,7 @@
         <v>12</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q114" s="1">
         <v>1</v>
@@ -7185,10 +7180,10 @@
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="1">
@@ -7199,7 +7194,7 @@
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -7211,7 +7206,7 @@
         <v>12</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q115" s="1">
         <v>1</v>
@@ -7224,10 +7219,10 @@
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D116" s="11"/>
       <c r="E116" s="1">
@@ -7238,7 +7233,7 @@
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -7250,7 +7245,7 @@
         <v>12</v>
       </c>
       <c r="P116" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q116" s="1">
         <v>1</v>
@@ -7263,10 +7258,10 @@
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D117" s="11"/>
       <c r="E117" s="1">
@@ -7277,7 +7272,7 @@
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -7289,7 +7284,7 @@
         <v>12</v>
       </c>
       <c r="P117" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q117" s="1">
         <v>1</v>
@@ -7302,10 +7297,10 @@
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D118" s="11"/>
       <c r="E118" s="1">
@@ -7316,7 +7311,7 @@
       </c>
       <c r="G118" s="1"/>
       <c r="H118" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
@@ -7328,7 +7323,7 @@
         <v>12</v>
       </c>
       <c r="P118" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q118" s="1">
         <v>1</v>
@@ -7341,10 +7336,10 @@
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="1">
@@ -7355,7 +7350,7 @@
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
@@ -7367,7 +7362,7 @@
         <v>12</v>
       </c>
       <c r="P119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q119" s="1">
         <v>2</v>
@@ -7380,10 +7375,10 @@
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D120" s="11"/>
       <c r="E120" s="1">
@@ -7394,7 +7389,7 @@
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
@@ -7406,7 +7401,7 @@
         <v>12</v>
       </c>
       <c r="P120" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q120" s="1">
         <v>2</v>
@@ -7419,10 +7414,10 @@
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D121" s="11"/>
       <c r="E121" s="1">
@@ -7433,7 +7428,7 @@
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
@@ -7445,7 +7440,7 @@
         <v>12</v>
       </c>
       <c r="P121" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q121" s="1">
         <v>4</v>
@@ -7458,10 +7453,10 @@
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D122" s="11"/>
       <c r="E122" s="1">
@@ -7472,7 +7467,7 @@
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
@@ -7484,7 +7479,7 @@
         <v>12</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q122" s="1">
         <v>2</v>
@@ -7497,10 +7492,10 @@
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D123" s="11"/>
       <c r="E123" s="1">
@@ -7511,7 +7506,7 @@
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
@@ -7523,7 +7518,7 @@
         <v>12</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q123" s="1">
         <v>1</v>
@@ -7536,10 +7531,10 @@
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D124" s="11"/>
       <c r="E124" s="1">
@@ -7550,7 +7545,7 @@
       </c>
       <c r="G124" s="1"/>
       <c r="H124" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
@@ -7562,7 +7557,7 @@
         <v>12</v>
       </c>
       <c r="P124" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q124" s="1">
         <v>1</v>
@@ -7575,10 +7570,10 @@
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D125" s="11"/>
       <c r="E125" s="1">
@@ -7589,7 +7584,7 @@
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
@@ -7601,7 +7596,7 @@
         <v>12</v>
       </c>
       <c r="P125" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q125" s="1">
         <v>1</v>
@@ -7614,10 +7609,10 @@
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D126" s="11"/>
       <c r="E126" s="1">
@@ -7628,7 +7623,7 @@
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
@@ -7640,7 +7635,7 @@
         <v>12</v>
       </c>
       <c r="P126" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q126" s="1">
         <v>1</v>
@@ -7653,10 +7648,10 @@
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D127" s="11"/>
       <c r="E127" s="1">
@@ -7667,7 +7662,7 @@
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
@@ -7679,7 +7674,7 @@
         <v>12</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q127" s="1">
         <v>1</v>
@@ -7692,10 +7687,10 @@
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D128" s="11"/>
       <c r="E128" s="1">
@@ -7706,7 +7701,7 @@
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
@@ -7718,7 +7713,7 @@
         <v>12</v>
       </c>
       <c r="P128" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q128" s="1">
         <v>1</v>
@@ -7731,10 +7726,10 @@
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D129" s="11"/>
       <c r="E129" s="1">
@@ -7745,7 +7740,7 @@
       </c>
       <c r="G129" s="1"/>
       <c r="H129" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -7757,7 +7752,7 @@
         <v>12</v>
       </c>
       <c r="P129" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q129" s="1">
         <v>1</v>
@@ -7770,10 +7765,10 @@
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D130" s="11"/>
       <c r="E130" s="1">
@@ -7784,7 +7779,7 @@
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -7796,7 +7791,7 @@
         <v>12</v>
       </c>
       <c r="P130" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q130" s="1">
         <v>1</v>
@@ -7809,10 +7804,10 @@
     <row r="131" spans="1:21" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D131" s="11">
         <v>3640</v>
@@ -7824,10 +7819,10 @@
         <v>0.2</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -7850,10 +7845,10 @@
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D132" s="12">
         <v>1055</v>
@@ -7865,10 +7860,10 @@
         <v>0.2</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -7889,10 +7884,10 @@
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D133" s="12">
         <v>3852</v>
@@ -7904,10 +7899,10 @@
         <v>0.2</v>
       </c>
       <c r="G133" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -7928,10 +7923,10 @@
     <row r="134" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D134" s="12">
         <v>4332</v>
@@ -7943,10 +7938,10 @@
         <v>0.2</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -7969,10 +7964,10 @@
     <row r="135" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D135" s="12">
         <v>6247</v>
@@ -7984,10 +7979,10 @@
         <v>0.2</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -8010,10 +8005,10 @@
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D136" s="12">
         <v>1185</v>
@@ -8025,10 +8020,10 @@
         <v>0.2</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -8049,10 +8044,10 @@
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D137" s="12">
         <v>1089</v>
@@ -8064,10 +8059,10 @@
         <v>0.2</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -8088,10 +8083,10 @@
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D138" s="12">
         <v>2918</v>
@@ -8103,10 +8098,10 @@
         <v>0.2</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -8127,10 +8122,10 @@
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="D139" s="12">
         <v>2680</v>
@@ -8142,10 +8137,10 @@
         <v>0.3</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -8166,10 +8161,10 @@
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="D140" s="12">
         <v>3192</v>
@@ -8181,10 +8176,10 @@
         <v>0.2</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -8205,10 +8200,10 @@
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="D141" s="12">
         <v>4972</v>
@@ -8220,10 +8215,10 @@
         <v>0.2</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -8244,10 +8239,10 @@
     <row r="142" spans="1:21" ht="105" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="D142" s="12">
         <v>9849</v>
@@ -8259,10 +8254,10 @@
         <v>0.2</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -8283,10 +8278,10 @@
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D143" s="12">
         <v>16233</v>
@@ -8298,10 +8293,10 @@
         <v>0.2</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -8322,10 +8317,10 @@
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D144" s="12">
         <v>3640</v>
@@ -8337,10 +8332,10 @@
         <v>0.2</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -8366,7 +8361,7 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
@@ -8414,7 +8409,7 @@
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
@@ -8439,7 +8434,7 @@
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
       <c r="G148" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -8464,7 +8459,7 @@
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -8489,7 +8484,7 @@
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -8514,7 +8509,7 @@
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -8539,7 +8534,7 @@
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -8564,7 +8559,7 @@
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
       <c r="G153" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -8589,7 +8584,7 @@
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -8614,7 +8609,7 @@
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -8639,7 +8634,7 @@
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
       <c r="G156" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -8664,7 +8659,7 @@
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
       <c r="G157" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
@@ -8707,10 +8702,10 @@
     <row r="159" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D159" s="11">
         <v>6997</v>
@@ -8722,10 +8717,10 @@
         <v>0.2</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -8774,7 +8769,7 @@
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="9" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
@@ -8799,7 +8794,7 @@
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
       <c r="G162" s="9" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
@@ -8824,7 +8819,7 @@
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
       <c r="G163" s="9" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
@@ -8849,7 +8844,7 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="9" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
@@ -8874,7 +8869,7 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="9" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
@@ -8899,7 +8894,7 @@
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="9" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
@@ -8924,7 +8919,7 @@
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="9" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
@@ -8949,7 +8944,7 @@
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
@@ -8974,7 +8969,7 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="9" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
@@ -8994,10 +8989,10 @@
     <row r="170" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D170" s="11">
         <v>7756</v>
@@ -9009,10 +9004,10 @@
         <v>0.2</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -9061,7 +9056,7 @@
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="9" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
@@ -9086,7 +9081,7 @@
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
       <c r="G173" s="9" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
@@ -9111,7 +9106,7 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="9" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
@@ -9136,7 +9131,7 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="9" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
@@ -9161,7 +9156,7 @@
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
       <c r="G176" s="9" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -9186,7 +9181,7 @@
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="9" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -9211,7 +9206,7 @@
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="9" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -9236,7 +9231,7 @@
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
@@ -9261,7 +9256,7 @@
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="9" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -9281,10 +9276,10 @@
     <row r="181" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D181" s="12">
         <v>3086</v>
@@ -9296,10 +9291,10 @@
         <v>0.2</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I181" s="1"/>
       <c r="J181" s="1"/>
@@ -9318,10 +9313,10 @@
     <row r="182" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D182" s="12">
         <v>4020</v>
@@ -9333,10 +9328,10 @@
         <v>0.2</v>
       </c>
       <c r="G182" s="9" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="I182" s="1"/>
       <c r="J182" s="1"/>
@@ -9355,10 +9350,10 @@
     <row r="183" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D183" s="12">
         <v>4605</v>
@@ -9370,10 +9365,10 @@
         <v>0.2</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="I183" s="1"/>
       <c r="J183" s="1"/>
@@ -9392,10 +9387,10 @@
     <row r="184" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D184" s="12">
         <v>734</v>
@@ -9407,10 +9402,10 @@
         <v>0.2</v>
       </c>
       <c r="G184" s="9" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
@@ -9429,10 +9424,10 @@
     <row r="185" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D185" s="12">
         <v>5311</v>
@@ -9444,10 +9439,10 @@
         <v>0.2</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
@@ -9471,7 +9466,7 @@
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="9" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
@@ -9496,7 +9491,7 @@
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="9" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
@@ -9521,7 +9516,7 @@
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="9" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
@@ -9546,7 +9541,7 @@
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
       <c r="G189" s="9" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
@@ -9571,7 +9566,7 @@
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="9" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
@@ -9596,7 +9591,7 @@
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="9" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
@@ -9621,7 +9616,7 @@
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="9" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
@@ -9646,7 +9641,7 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="8" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
@@ -9666,10 +9661,10 @@
     <row r="194" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D194" s="11">
         <v>3213</v>
@@ -9681,10 +9676,10 @@
         <v>0.2</v>
       </c>
       <c r="G194" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
@@ -9708,7 +9703,7 @@
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="8" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
@@ -9733,7 +9728,7 @@
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="9" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
@@ -9758,7 +9753,7 @@
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="9" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>

--- a/tabela_produtos_site.xlsx
+++ b/tabela_produtos_site.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0925d356f97d17c9/Desktop/special-summer-sale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="11_1479D0EED2335F840378C78657AD3C1B78FA1F78" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE56C006-6895-4636-BA08-D53162748D67}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="11_1479D0EED2335F840378C78657AD3C1B78FA1F78" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{488128B3-D6A2-4B33-AE83-900A21C6F11A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2162,6 +2161,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2267,13 +2269,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3966,9 +3968,7 @@
       <c r="D35" s="11">
         <v>1450</v>
       </c>
-      <c r="E35" s="1">
-        <v>870</v>
-      </c>
+      <c r="E35" s="1"/>
       <c r="F35" s="1">
         <v>0.3</v>
       </c>
@@ -4007,9 +4007,7 @@
       <c r="D36" s="11">
         <v>3614</v>
       </c>
-      <c r="E36" s="1">
-        <v>1445.6</v>
-      </c>
+      <c r="E36" s="1"/>
       <c r="F36" s="1">
         <v>0.6</v>
       </c>
@@ -4048,9 +4046,7 @@
       <c r="D37" s="11">
         <v>6624</v>
       </c>
-      <c r="E37" s="1">
-        <v>2649.6</v>
-      </c>
+      <c r="E37" s="1"/>
       <c r="F37" s="1">
         <v>0.6</v>
       </c>
@@ -4089,9 +4085,7 @@
       <c r="D38" s="11">
         <v>6350</v>
       </c>
-      <c r="E38" s="1">
-        <v>2540</v>
-      </c>
+      <c r="E38" s="1"/>
       <c r="F38" s="1">
         <v>0.6</v>
       </c>
@@ -4130,9 +4124,7 @@
       <c r="D39" s="11">
         <v>3734</v>
       </c>
-      <c r="E39" s="1">
-        <v>1493.6</v>
-      </c>
+      <c r="E39" s="1"/>
       <c r="F39" s="1">
         <v>0.6</v>
       </c>
@@ -4171,9 +4163,7 @@
       <c r="D40" s="11">
         <v>2890</v>
       </c>
-      <c r="E40" s="1">
-        <v>1156</v>
-      </c>
+      <c r="E40" s="1"/>
       <c r="F40" s="1">
         <v>0.6</v>
       </c>
@@ -4212,9 +4202,7 @@
       <c r="D41" s="11">
         <v>3455</v>
       </c>
-      <c r="E41" s="1">
-        <v>1382</v>
-      </c>
+      <c r="E41" s="1"/>
       <c r="F41" s="1">
         <v>0.6</v>
       </c>
@@ -4253,9 +4241,7 @@
       <c r="D42" s="11">
         <v>8700</v>
       </c>
-      <c r="E42" s="1">
-        <v>3480</v>
-      </c>
+      <c r="E42" s="1"/>
       <c r="F42" s="1">
         <v>0.4</v>
       </c>
@@ -4294,9 +4280,7 @@
       <c r="D43" s="11">
         <v>4525</v>
       </c>
-      <c r="E43" s="1">
-        <v>2715</v>
-      </c>
+      <c r="E43" s="1"/>
       <c r="F43" s="1">
         <v>0.4</v>
       </c>
@@ -4335,9 +4319,7 @@
       <c r="D44" s="11">
         <v>2750</v>
       </c>
-      <c r="E44" s="1">
-        <v>1650</v>
-      </c>
+      <c r="E44" s="1"/>
       <c r="F44" s="1">
         <v>0.3</v>
       </c>
@@ -4378,9 +4360,7 @@
       <c r="D45" s="11">
         <v>1300</v>
       </c>
-      <c r="E45" s="1">
-        <v>909.99999999999989</v>
-      </c>
+      <c r="E45" s="1"/>
       <c r="F45" s="1">
         <v>0.2</v>
       </c>
@@ -4419,9 +4399,7 @@
       <c r="D46" s="11">
         <v>5880</v>
       </c>
-      <c r="E46" s="1">
-        <v>2640</v>
-      </c>
+      <c r="E46" s="1"/>
       <c r="F46" s="1">
         <v>0.5</v>
       </c>
@@ -4462,9 +4440,7 @@
       <c r="D47" s="11">
         <v>1455</v>
       </c>
-      <c r="E47" s="1">
-        <v>727.5</v>
-      </c>
+      <c r="E47" s="1"/>
       <c r="F47" s="1">
         <v>0.4</v>
       </c>
@@ -4501,9 +4477,7 @@
       <c r="D48" s="11">
         <v>3360</v>
       </c>
-      <c r="E48" s="1">
-        <v>2352</v>
-      </c>
+      <c r="E48" s="1"/>
       <c r="F48" s="1">
         <v>0.3</v>
       </c>
@@ -4542,11 +4516,9 @@
         <v>185</v>
       </c>
       <c r="D49" s="11">
-        <v>2600</v>
-      </c>
-      <c r="E49" s="1">
-        <v>1300</v>
-      </c>
+        <v>2980</v>
+      </c>
+      <c r="E49" s="1"/>
       <c r="F49" s="1">
         <v>0.5</v>
       </c>
@@ -4583,11 +4555,9 @@
         <v>188</v>
       </c>
       <c r="D50" s="11">
-        <v>2700</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1350</v>
-      </c>
+        <v>2980</v>
+      </c>
+      <c r="E50" s="1"/>
       <c r="F50" s="1">
         <v>0.5</v>
       </c>
@@ -4626,9 +4596,7 @@
       <c r="D51" s="11">
         <v>1752</v>
       </c>
-      <c r="E51" s="1">
-        <v>700.80000000000007</v>
-      </c>
+      <c r="E51" s="1"/>
       <c r="F51" s="1">
         <v>0.4</v>
       </c>
@@ -4667,9 +4635,7 @@
       <c r="D52" s="11">
         <v>1590</v>
       </c>
-      <c r="E52" s="1">
-        <v>636</v>
-      </c>
+      <c r="E52" s="1"/>
       <c r="F52" s="1">
         <v>0.4</v>
       </c>
@@ -4708,9 +4674,7 @@
       <c r="D53" s="11">
         <v>1590</v>
       </c>
-      <c r="E53" s="1">
-        <v>954</v>
-      </c>
+      <c r="E53" s="1"/>
       <c r="F53" s="1">
         <v>0.3</v>
       </c>
@@ -4749,9 +4713,7 @@
       <c r="D54" s="11">
         <v>1590</v>
       </c>
-      <c r="E54" s="1">
-        <v>795</v>
-      </c>
+      <c r="E54" s="1"/>
       <c r="F54" s="1">
         <v>0.4</v>
       </c>
@@ -4790,9 +4752,7 @@
       <c r="D55" s="11">
         <v>1752</v>
       </c>
-      <c r="E55" s="1">
-        <v>1051.2</v>
-      </c>
+      <c r="E55" s="1"/>
       <c r="F55" s="1">
         <v>0.4</v>
       </c>
@@ -4831,9 +4791,7 @@
       <c r="D56" s="11">
         <v>1560</v>
       </c>
-      <c r="E56" s="1">
-        <v>780</v>
-      </c>
+      <c r="E56" s="1"/>
       <c r="F56" s="1">
         <v>0.4</v>
       </c>
@@ -4872,9 +4830,7 @@
       <c r="D57" s="11">
         <v>2980</v>
       </c>
-      <c r="E57" s="1">
-        <v>1192</v>
-      </c>
+      <c r="E57" s="1"/>
       <c r="F57" s="1">
         <v>0.5</v>
       </c>
@@ -4913,9 +4869,7 @@
       <c r="D58" s="11">
         <v>3745</v>
       </c>
-      <c r="E58" s="1">
-        <v>1872.5</v>
-      </c>
+      <c r="E58" s="1"/>
       <c r="F58" s="1">
         <v>0.5</v>
       </c>
@@ -4954,9 +4908,7 @@
       <c r="D59" s="11">
         <v>2980</v>
       </c>
-      <c r="E59" s="1">
-        <v>1490</v>
-      </c>
+      <c r="E59" s="1"/>
       <c r="F59" s="1">
         <v>0.5</v>
       </c>
@@ -4997,9 +4949,7 @@
       <c r="D60" s="11">
         <v>980</v>
       </c>
-      <c r="E60" s="1">
-        <v>588</v>
-      </c>
+      <c r="E60" s="1"/>
       <c r="F60" s="1">
         <v>0.4</v>
       </c>
@@ -5040,9 +4990,7 @@
       <c r="D61" s="11">
         <v>3700</v>
       </c>
-      <c r="E61" s="1">
-        <v>1850</v>
-      </c>
+      <c r="E61" s="1"/>
       <c r="F61" s="1">
         <v>0.5</v>
       </c>
@@ -5081,9 +5029,7 @@
       <c r="D62" s="11">
         <v>670</v>
       </c>
-      <c r="E62" s="1">
-        <v>468.99999999999989</v>
-      </c>
+      <c r="E62" s="1"/>
       <c r="F62" s="1">
         <v>0.3</v>
       </c>
@@ -5122,9 +5068,7 @@
       <c r="D63" s="11">
         <v>1803</v>
       </c>
-      <c r="E63" s="1">
-        <v>1262.0999999999999</v>
-      </c>
+      <c r="E63" s="1"/>
       <c r="F63" s="1">
         <v>0.2</v>
       </c>
@@ -5163,9 +5107,7 @@
       <c r="D64" s="11">
         <v>1595</v>
       </c>
-      <c r="E64" s="1">
-        <v>1116.5</v>
-      </c>
+      <c r="E64" s="1"/>
       <c r="F64" s="1">
         <v>0.2</v>
       </c>
@@ -5204,9 +5146,7 @@
       <c r="D65" s="11">
         <v>6070</v>
       </c>
-      <c r="E65" s="1">
-        <v>2428</v>
-      </c>
+      <c r="E65" s="1"/>
       <c r="F65" s="1">
         <v>0.6</v>
       </c>
@@ -5245,9 +5185,7 @@
       <c r="D66" s="11">
         <v>28588</v>
       </c>
-      <c r="E66" s="1">
-        <v>11435.2</v>
-      </c>
+      <c r="E66" s="1"/>
       <c r="F66" s="1">
         <v>0.5</v>
       </c>
@@ -5286,11 +5224,9 @@
       <c r="D67" s="11">
         <v>9674</v>
       </c>
-      <c r="E67" s="1">
-        <v>6771.7999999999993</v>
-      </c>
+      <c r="E67" s="1"/>
       <c r="F67" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
@@ -5329,11 +5265,9 @@
       <c r="D68" s="11">
         <v>16358</v>
       </c>
-      <c r="E68" s="1">
-        <v>8179</v>
-      </c>
+      <c r="E68" s="1"/>
       <c r="F68" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
@@ -5372,9 +5306,7 @@
       <c r="D69" s="11">
         <v>7570</v>
       </c>
-      <c r="E69" s="1">
-        <v>3028</v>
-      </c>
+      <c r="E69" s="1"/>
       <c r="F69" s="1">
         <v>0.5</v>
       </c>
@@ -6249,10 +6181,10 @@
       <c r="C91" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D91" s="11"/>
-      <c r="E91" s="1">
-        <v>1992</v>
-      </c>
+      <c r="D91" s="11">
+        <v>4980</v>
+      </c>
+      <c r="E91" s="1"/>
       <c r="F91" s="1">
         <v>0.6</v>
       </c>
@@ -6288,10 +6220,10 @@
       <c r="C92" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D92" s="11"/>
-      <c r="E92" s="1">
-        <v>864.5</v>
-      </c>
+      <c r="D92" s="11">
+        <v>1720</v>
+      </c>
+      <c r="E92" s="1"/>
       <c r="F92" s="1">
         <v>0.4</v>
       </c>
@@ -6327,12 +6259,12 @@
       <c r="C93" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D93" s="11"/>
-      <c r="E93" s="1">
-        <v>717.5</v>
-      </c>
+      <c r="D93" s="11">
+        <v>1435</v>
+      </c>
+      <c r="E93" s="1"/>
       <c r="F93" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1" t="s">
@@ -6366,10 +6298,10 @@
       <c r="C94" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D94" s="11"/>
-      <c r="E94" s="1">
-        <v>2252.5</v>
-      </c>
+      <c r="D94" s="11">
+        <v>3980</v>
+      </c>
+      <c r="E94" s="1"/>
       <c r="F94" s="1">
         <v>0.5</v>
       </c>
@@ -6405,10 +6337,10 @@
       <c r="C95" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D95" s="11"/>
-      <c r="E95" s="1">
-        <v>1475</v>
-      </c>
+      <c r="D95" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E95" s="1"/>
       <c r="F95" s="1">
         <v>0.4</v>
       </c>
@@ -6444,10 +6376,10 @@
       <c r="C96" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D96" s="11"/>
-      <c r="E96" s="1">
-        <v>2283.6</v>
-      </c>
+      <c r="D96" s="11">
+        <v>3806</v>
+      </c>
+      <c r="E96" s="1"/>
       <c r="F96" s="1">
         <v>0.4</v>
       </c>
@@ -6483,12 +6415,12 @@
       <c r="C97" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D97" s="11"/>
-      <c r="E97" s="1">
-        <v>820</v>
-      </c>
+      <c r="D97" s="11">
+        <v>1640</v>
+      </c>
+      <c r="E97" s="1"/>
       <c r="F97" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="1" t="s">
@@ -6522,12 +6454,12 @@
       <c r="C98" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D98" s="11"/>
-      <c r="E98" s="1">
-        <v>872.5</v>
-      </c>
+      <c r="D98" s="11">
+        <v>1745</v>
+      </c>
+      <c r="E98" s="1"/>
       <c r="F98" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
@@ -6561,12 +6493,12 @@
       <c r="C99" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D99" s="11"/>
-      <c r="E99" s="1">
-        <v>711.5</v>
-      </c>
+      <c r="D99" s="11">
+        <v>1423</v>
+      </c>
+      <c r="E99" s="1"/>
       <c r="F99" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1" t="s">
@@ -6600,12 +6532,12 @@
       <c r="C100" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D100" s="11"/>
-      <c r="E100" s="1">
-        <v>578.5</v>
-      </c>
+      <c r="D100" s="11">
+        <v>1157</v>
+      </c>
+      <c r="E100" s="1"/>
       <c r="F100" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G100" s="1"/>
       <c r="H100" s="1" t="s">
@@ -6639,10 +6571,10 @@
       <c r="C101" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D101" s="11"/>
-      <c r="E101" s="1">
-        <v>819.69999999999993</v>
-      </c>
+      <c r="D101" s="11">
+        <v>1289</v>
+      </c>
+      <c r="E101" s="1"/>
       <c r="F101" s="1">
         <v>0.3</v>
       </c>
@@ -6678,10 +6610,10 @@
       <c r="C102" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D102" s="11"/>
-      <c r="E102" s="1">
-        <v>2244.1999999999998</v>
-      </c>
+      <c r="D102" s="11">
+        <v>3206</v>
+      </c>
+      <c r="E102" s="1"/>
       <c r="F102" s="1">
         <v>0.3</v>
       </c>
@@ -6717,10 +6649,10 @@
       <c r="C103" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D103" s="11"/>
-      <c r="E103" s="1">
-        <v>2939.2</v>
-      </c>
+      <c r="D103" s="11">
+        <v>7348</v>
+      </c>
+      <c r="E103" s="1"/>
       <c r="F103" s="1">
         <v>0.6</v>
       </c>
@@ -6756,10 +6688,10 @@
       <c r="C104" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D104" s="11"/>
-      <c r="E104" s="1">
-        <v>3423</v>
-      </c>
+      <c r="D104" s="11">
+        <v>4890</v>
+      </c>
+      <c r="E104" s="1"/>
       <c r="F104" s="1">
         <v>0.3</v>
       </c>
@@ -6795,10 +6727,10 @@
       <c r="C105" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D105" s="11"/>
-      <c r="E105" s="1">
-        <v>3671.5</v>
-      </c>
+      <c r="D105" s="11">
+        <v>5245</v>
+      </c>
+      <c r="E105" s="1"/>
       <c r="F105" s="1">
         <v>0.3</v>
       </c>
@@ -6834,10 +6766,10 @@
       <c r="C106" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D106" s="11"/>
-      <c r="E106" s="1">
-        <v>2590</v>
-      </c>
+      <c r="D106" s="11">
+        <v>3700</v>
+      </c>
+      <c r="E106" s="1"/>
       <c r="F106" s="1">
         <v>0.3</v>
       </c>
@@ -6873,10 +6805,10 @@
       <c r="C107" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D107" s="11"/>
-      <c r="E107" s="1">
-        <v>1160</v>
-      </c>
+      <c r="D107" s="11">
+        <v>2900</v>
+      </c>
+      <c r="E107" s="1"/>
       <c r="F107" s="1">
         <v>0.6</v>
       </c>
@@ -6912,12 +6844,12 @@
       <c r="C108" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D108" s="11"/>
-      <c r="E108" s="1">
-        <v>562.5</v>
-      </c>
+      <c r="D108" s="11">
+        <v>1125</v>
+      </c>
+      <c r="E108" s="1"/>
       <c r="F108" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
@@ -6951,12 +6883,12 @@
       <c r="C109" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D109" s="11"/>
-      <c r="E109" s="1">
-        <v>68.599999999999994</v>
-      </c>
+      <c r="D109" s="11">
+        <v>98</v>
+      </c>
+      <c r="E109" s="1"/>
       <c r="F109" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1" t="s">
@@ -6990,10 +6922,10 @@
       <c r="C110" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D110" s="11"/>
-      <c r="E110" s="1">
-        <v>298.8</v>
-      </c>
+      <c r="D110" s="11">
+        <v>498</v>
+      </c>
+      <c r="E110" s="1"/>
       <c r="F110" s="1">
         <v>0.4</v>
       </c>
@@ -7029,10 +6961,10 @@
       <c r="C111" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D111" s="11"/>
-      <c r="E111" s="1">
-        <v>348.6</v>
-      </c>
+      <c r="D111" s="11">
+        <v>498</v>
+      </c>
+      <c r="E111" s="1"/>
       <c r="F111" s="1">
         <v>0.3</v>
       </c>
@@ -7068,12 +7000,12 @@
       <c r="C112" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D112" s="11"/>
-      <c r="E112" s="1">
-        <v>187.5</v>
-      </c>
+      <c r="D112" s="11">
+        <v>395</v>
+      </c>
+      <c r="E112" s="1"/>
       <c r="F112" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1" t="s">
@@ -7107,10 +7039,10 @@
       <c r="C113" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D113" s="11"/>
-      <c r="E113" s="1">
-        <v>688.19999999999993</v>
-      </c>
+      <c r="D113" s="11">
+        <v>1147</v>
+      </c>
+      <c r="E113" s="1"/>
       <c r="F113" s="1">
         <v>0.4</v>
       </c>
@@ -7146,10 +7078,10 @@
       <c r="C114" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D114" s="11"/>
-      <c r="E114" s="1">
-        <v>613.19999999999993</v>
-      </c>
+      <c r="D114" s="11">
+        <v>1022</v>
+      </c>
+      <c r="E114" s="1"/>
       <c r="F114" s="1">
         <v>0.4</v>
       </c>
@@ -7185,10 +7117,10 @@
       <c r="C115" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="1">
-        <v>561</v>
-      </c>
+      <c r="D115" s="11">
+        <v>1122</v>
+      </c>
+      <c r="E115" s="1"/>
       <c r="F115" s="1">
         <v>0.5</v>
       </c>
@@ -7224,10 +7156,10 @@
       <c r="C116" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D116" s="11"/>
-      <c r="E116" s="1">
-        <v>1253</v>
-      </c>
+      <c r="D116" s="11">
+        <v>1790</v>
+      </c>
+      <c r="E116" s="1"/>
       <c r="F116" s="1">
         <v>0.3</v>
       </c>
@@ -7263,10 +7195,10 @@
       <c r="C117" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D117" s="11"/>
-      <c r="E117" s="1">
-        <v>1253</v>
-      </c>
+      <c r="D117" s="11">
+        <v>1790</v>
+      </c>
+      <c r="E117" s="1"/>
       <c r="F117" s="1">
         <v>0.3</v>
       </c>
@@ -7302,10 +7234,10 @@
       <c r="C118" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D118" s="11"/>
-      <c r="E118" s="1">
-        <v>1253</v>
-      </c>
+      <c r="D118" s="11">
+        <v>1790</v>
+      </c>
+      <c r="E118" s="1"/>
       <c r="F118" s="1">
         <v>0.3</v>
       </c>
@@ -7341,10 +7273,10 @@
       <c r="C119" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="1">
-        <v>284.89999999999998</v>
-      </c>
+      <c r="D119" s="11">
+        <v>407</v>
+      </c>
+      <c r="E119" s="1"/>
       <c r="F119" s="1">
         <v>0.3</v>
       </c>
@@ -7380,10 +7312,10 @@
       <c r="C120" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D120" s="11"/>
-      <c r="E120" s="1">
-        <v>284.89999999999998</v>
-      </c>
+      <c r="D120" s="11">
+        <v>407</v>
+      </c>
+      <c r="E120" s="1"/>
       <c r="F120" s="1">
         <v>0.3</v>
       </c>
@@ -7419,10 +7351,10 @@
       <c r="C121" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D121" s="11"/>
-      <c r="E121" s="1">
-        <v>880.8</v>
-      </c>
+      <c r="D121" s="11">
+        <v>1468</v>
+      </c>
+      <c r="E121" s="1"/>
       <c r="F121" s="1">
         <v>0.4</v>
       </c>
@@ -7458,10 +7390,10 @@
       <c r="C122" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D122" s="11"/>
-      <c r="E122" s="1">
-        <v>1438</v>
-      </c>
+      <c r="D122" s="11">
+        <v>3595</v>
+      </c>
+      <c r="E122" s="1"/>
       <c r="F122" s="1">
         <v>0.6</v>
       </c>
@@ -7497,10 +7429,10 @@
       <c r="C123" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D123" s="11"/>
-      <c r="E123" s="1">
-        <v>520</v>
-      </c>
+      <c r="D123" s="11">
+        <v>1300</v>
+      </c>
+      <c r="E123" s="1"/>
       <c r="F123" s="1">
         <v>0.6</v>
       </c>
@@ -7536,10 +7468,10 @@
       <c r="C124" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D124" s="11"/>
-      <c r="E124" s="1">
-        <v>1192</v>
-      </c>
+      <c r="D124" s="11">
+        <v>2980</v>
+      </c>
+      <c r="E124" s="1"/>
       <c r="F124" s="1">
         <v>0.6</v>
       </c>
@@ -7575,10 +7507,10 @@
       <c r="C125" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D125" s="11"/>
-      <c r="E125" s="1">
-        <v>3390</v>
-      </c>
+      <c r="D125" s="11">
+        <v>6780</v>
+      </c>
+      <c r="E125" s="1"/>
       <c r="F125" s="1">
         <v>0.5</v>
       </c>
@@ -7614,10 +7546,10 @@
       <c r="C126" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D126" s="11"/>
-      <c r="E126" s="1">
-        <v>1750</v>
-      </c>
+      <c r="D126" s="11">
+        <v>3500</v>
+      </c>
+      <c r="E126" s="1"/>
       <c r="F126" s="1">
         <v>0.5</v>
       </c>
@@ -7653,10 +7585,10 @@
       <c r="C127" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D127" s="11"/>
-      <c r="E127" s="1">
-        <v>1992</v>
-      </c>
+      <c r="D127" s="11">
+        <v>4980</v>
+      </c>
+      <c r="E127" s="1"/>
       <c r="F127" s="1">
         <v>0.6</v>
       </c>
@@ -7692,10 +7624,10 @@
       <c r="C128" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D128" s="11"/>
-      <c r="E128" s="1">
-        <v>1992</v>
-      </c>
+      <c r="D128" s="11">
+        <v>4980</v>
+      </c>
+      <c r="E128" s="1"/>
       <c r="F128" s="1">
         <v>0.6</v>
       </c>
@@ -7731,10 +7663,10 @@
       <c r="C129" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D129" s="11"/>
-      <c r="E129" s="1">
-        <v>2880</v>
-      </c>
+      <c r="D129" s="11">
+        <v>5860</v>
+      </c>
+      <c r="E129" s="1"/>
       <c r="F129" s="1">
         <v>0.5</v>
       </c>
@@ -7770,10 +7702,10 @@
       <c r="C130" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D130" s="11"/>
-      <c r="E130" s="1">
-        <v>2300.9</v>
-      </c>
+      <c r="D130" s="11">
+        <v>3287</v>
+      </c>
+      <c r="E130" s="1"/>
       <c r="F130" s="1">
         <v>0.3</v>
       </c>
@@ -7812,9 +7744,7 @@
       <c r="D131" s="11">
         <v>3640</v>
       </c>
-      <c r="E131" s="1">
-        <v>3640</v>
-      </c>
+      <c r="E131" s="1"/>
       <c r="F131" s="1">
         <v>0.2</v>
       </c>
@@ -7853,9 +7783,7 @@
       <c r="D132" s="12">
         <v>1055</v>
       </c>
-      <c r="E132" s="1">
-        <v>1055</v>
-      </c>
+      <c r="E132" s="1"/>
       <c r="F132" s="1">
         <v>0.2</v>
       </c>
@@ -7892,9 +7820,7 @@
       <c r="D133" s="12">
         <v>3852</v>
       </c>
-      <c r="E133" s="1">
-        <v>3852</v>
-      </c>
+      <c r="E133" s="1"/>
       <c r="F133" s="1">
         <v>0.2</v>
       </c>
@@ -7931,9 +7857,7 @@
       <c r="D134" s="12">
         <v>4332</v>
       </c>
-      <c r="E134" s="1">
-        <v>4332</v>
-      </c>
+      <c r="E134" s="1"/>
       <c r="F134" s="1">
         <v>0.2</v>
       </c>
@@ -7972,9 +7896,7 @@
       <c r="D135" s="12">
         <v>6247</v>
       </c>
-      <c r="E135" s="1">
-        <v>6247</v>
-      </c>
+      <c r="E135" s="1"/>
       <c r="F135" s="1">
         <v>0.2</v>
       </c>
@@ -8013,9 +7935,7 @@
       <c r="D136" s="12">
         <v>1185</v>
       </c>
-      <c r="E136" s="1">
-        <v>1185</v>
-      </c>
+      <c r="E136" s="1"/>
       <c r="F136" s="1">
         <v>0.2</v>
       </c>
@@ -8052,9 +7972,7 @@
       <c r="D137" s="12">
         <v>1089</v>
       </c>
-      <c r="E137" s="1">
-        <v>1089</v>
-      </c>
+      <c r="E137" s="1"/>
       <c r="F137" s="1">
         <v>0.2</v>
       </c>
@@ -8091,9 +8009,7 @@
       <c r="D138" s="12">
         <v>2918</v>
       </c>
-      <c r="E138" s="1">
-        <v>2918</v>
-      </c>
+      <c r="E138" s="1"/>
       <c r="F138" s="1">
         <v>0.2</v>
       </c>
@@ -8130,9 +8046,7 @@
       <c r="D139" s="12">
         <v>2680</v>
       </c>
-      <c r="E139" s="1">
-        <v>2680</v>
-      </c>
+      <c r="E139" s="1"/>
       <c r="F139" s="1">
         <v>0.3</v>
       </c>
@@ -8169,9 +8083,7 @@
       <c r="D140" s="12">
         <v>3192</v>
       </c>
-      <c r="E140" s="1">
-        <v>3192</v>
-      </c>
+      <c r="E140" s="1"/>
       <c r="F140" s="1">
         <v>0.2</v>
       </c>
@@ -8208,9 +8120,7 @@
       <c r="D141" s="12">
         <v>4972</v>
       </c>
-      <c r="E141" s="1">
-        <v>4972</v>
-      </c>
+      <c r="E141" s="1"/>
       <c r="F141" s="1">
         <v>0.2</v>
       </c>
@@ -8247,9 +8157,7 @@
       <c r="D142" s="12">
         <v>9849</v>
       </c>
-      <c r="E142" s="1">
-        <v>9849</v>
-      </c>
+      <c r="E142" s="1"/>
       <c r="F142" s="1">
         <v>0.2</v>
       </c>
@@ -8286,9 +8194,7 @@
       <c r="D143" s="12">
         <v>16233</v>
       </c>
-      <c r="E143" s="1">
-        <v>16233</v>
-      </c>
+      <c r="E143" s="1"/>
       <c r="F143" s="1">
         <v>0.2</v>
       </c>
@@ -8325,9 +8231,7 @@
       <c r="D144" s="12">
         <v>3640</v>
       </c>
-      <c r="E144" s="1">
-        <v>3640</v>
-      </c>
+      <c r="E144" s="1"/>
       <c r="F144" s="1">
         <v>0.2</v>
       </c>
@@ -8710,9 +8614,7 @@
       <c r="D159" s="11">
         <v>6997</v>
       </c>
-      <c r="E159" s="1">
-        <v>6997</v>
-      </c>
+      <c r="E159" s="1"/>
       <c r="F159" s="1">
         <v>0.2</v>
       </c>
@@ -8997,9 +8899,7 @@
       <c r="D170" s="11">
         <v>7756</v>
       </c>
-      <c r="E170" s="1">
-        <v>7756</v>
-      </c>
+      <c r="E170" s="1"/>
       <c r="F170" s="1">
         <v>0.2</v>
       </c>
@@ -9284,9 +9184,7 @@
       <c r="D181" s="12">
         <v>3086</v>
       </c>
-      <c r="E181" s="1">
-        <v>3086</v>
-      </c>
+      <c r="E181" s="1"/>
       <c r="F181" s="1">
         <v>0.2</v>
       </c>
@@ -9321,9 +9219,7 @@
       <c r="D182" s="12">
         <v>4020</v>
       </c>
-      <c r="E182" s="1">
-        <v>4020</v>
-      </c>
+      <c r="E182" s="1"/>
       <c r="F182" s="1">
         <v>0.2</v>
       </c>
@@ -9358,9 +9254,7 @@
       <c r="D183" s="12">
         <v>4605</v>
       </c>
-      <c r="E183" s="1">
-        <v>4605</v>
-      </c>
+      <c r="E183" s="1"/>
       <c r="F183" s="1">
         <v>0.2</v>
       </c>
@@ -9395,9 +9289,7 @@
       <c r="D184" s="12">
         <v>734</v>
       </c>
-      <c r="E184" s="1">
-        <v>734</v>
-      </c>
+      <c r="E184" s="1"/>
       <c r="F184" s="1">
         <v>0.2</v>
       </c>
@@ -9432,9 +9324,7 @@
       <c r="D185" s="12">
         <v>5311</v>
       </c>
-      <c r="E185" s="1">
-        <v>5311</v>
-      </c>
+      <c r="E185" s="1"/>
       <c r="F185" s="1">
         <v>0.2</v>
       </c>
@@ -9669,9 +9559,7 @@
       <c r="D194" s="11">
         <v>3213</v>
       </c>
-      <c r="E194" s="1">
-        <v>3213</v>
-      </c>
+      <c r="E194" s="1"/>
       <c r="F194" s="1">
         <v>0.2</v>
       </c>
